--- a/output/roomself_excel/13426.xlsx
+++ b/output/roomself_excel/13426.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>252447</v>
+        <v>29596</v>
       </c>
       <c r="D2" t="n">
-        <v>4124</v>
+        <v>1480</v>
       </c>
       <c r="E2" t="n">
-        <v>979</v>
+        <v>152</v>
       </c>
       <c r="F2" t="n">
-        <v>445</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>42903</v>
+        <v>252447</v>
       </c>
       <c r="D3" t="n">
-        <v>1860</v>
+        <v>4124</v>
       </c>
       <c r="E3" t="n">
+        <v>652</v>
+      </c>
+      <c r="F3" t="n">
         <v>445</v>
-      </c>
-      <c r="F3" t="n">
-        <v>316</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>29596</v>
+        <v>42903</v>
       </c>
       <c r="D4" t="n">
-        <v>1480</v>
+        <v>1860</v>
       </c>
       <c r="E4" t="n">
-        <v>445</v>
+        <v>316</v>
       </c>
       <c r="F4" t="n">
-        <v>152</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5">

--- a/output/roomself_excel/13426.xlsx
+++ b/output/roomself_excel/13426.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>1480</v>
       </c>
-      <c r="E2" t="n">
-        <v>152</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>81</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>4124</v>
       </c>
-      <c r="E3" t="n">
-        <v>652</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>445</v>
+        <v>401</v>
+      </c>
+      <c r="G3" t="n">
+        <v>22</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1259</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>1860</v>
       </c>
-      <c r="E4" t="n">
-        <v>316</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>193</v>
+        <v>272</v>
+      </c>
+      <c r="G4" t="n">
+        <v>22</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>149</v>
+      </c>
+      <c r="J4" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -541,11 +601,27 @@
       <c r="D5" t="n">
         <v>1396</v>
       </c>
-      <c r="E5" t="n">
-        <v>240</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>153</v>
+        <v>131</v>
+      </c>
+      <c r="G5" t="n">
+        <v>22</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>218</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
